--- a/api/placeholders/RifResistanceRate.xlsx
+++ b/api/placeholders/RifResistanceRate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aepel\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\systemoneid\aspect\api\placeholders\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Deployment Name</t>
   </si>
@@ -53,94 +53,70 @@
     <t>County</t>
   </si>
   <si>
-    <t>Deployment 1</t>
-  </si>
-  <si>
-    <t>Deployment 2</t>
-  </si>
-  <si>
-    <t>Deployment 3</t>
-  </si>
-  <si>
-    <t>Deployment 4</t>
-  </si>
-  <si>
-    <t>Deployment 5</t>
-  </si>
-  <si>
-    <t>Deployment 6</t>
-  </si>
-  <si>
-    <t>Deployment 7</t>
-  </si>
-  <si>
-    <t>Deployment 8</t>
-  </si>
-  <si>
-    <t>Deployment 9</t>
-  </si>
-  <si>
-    <t>Deployment 10</t>
-  </si>
-  <si>
-    <t>State 1</t>
-  </si>
-  <si>
-    <t>State 2</t>
-  </si>
-  <si>
-    <t>State 3</t>
-  </si>
-  <si>
-    <t>State 4</t>
-  </si>
-  <si>
-    <t>State 5</t>
-  </si>
-  <si>
-    <t>State 6</t>
-  </si>
-  <si>
-    <t>State 7</t>
-  </si>
-  <si>
-    <t>State 8</t>
-  </si>
-  <si>
-    <t>State 9</t>
-  </si>
-  <si>
-    <t>State 10</t>
-  </si>
-  <si>
-    <t>County 1</t>
-  </si>
-  <si>
-    <t>County 2</t>
-  </si>
-  <si>
-    <t>County 3</t>
-  </si>
-  <si>
-    <t>County 4</t>
-  </si>
-  <si>
-    <t>County 5</t>
-  </si>
-  <si>
-    <t>County 6</t>
-  </si>
-  <si>
-    <t>County 7</t>
-  </si>
-  <si>
-    <t>County 8</t>
-  </si>
-  <si>
-    <t>County 9</t>
-  </si>
-  <si>
-    <t>County 10</t>
+    <t>Shelburne Falls ML</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Hampshire County</t>
+  </si>
+  <si>
+    <t>Akron ML</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Summit County</t>
+  </si>
+  <si>
+    <t>Boston Micro</t>
+  </si>
+  <si>
+    <t>Suffolk County</t>
+  </si>
+  <si>
+    <t>Philadelphia ML</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Philadelphia County</t>
+  </si>
+  <si>
+    <t>Pittsburgh ML</t>
+  </si>
+  <si>
+    <t>Allegheny County</t>
+  </si>
+  <si>
+    <t>Northampton ML</t>
+  </si>
+  <si>
+    <t>Wooster ML</t>
+  </si>
+  <si>
+    <t>Wayne County</t>
+  </si>
+  <si>
+    <t>Atlanta ML</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Fulton County</t>
+  </si>
+  <si>
+    <t>Cleveland ML</t>
+  </si>
+  <si>
+    <t>Cuyahoga County</t>
+  </si>
+  <si>
+    <t>Wooster Hospital</t>
   </si>
 </sst>
 </file>
@@ -149,14 +125,6 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -188,6 +156,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -198,32 +172,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF3CC0DD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -246,7 +204,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -255,14 +213,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -270,161 +230,153 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
@@ -812,7 +764,7 @@
     <col min="1" max="3" width="27.08203125" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" style="3" customWidth="1"/>
     <col min="5" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -836,26 +788,26 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="31" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="38" t="s">
         <v>5</v>
       </c>
     </row>
@@ -864,229 +816,229 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1927</v>
+      </c>
+      <c r="E8" s="5">
+        <v>200</v>
+      </c>
+      <c r="F8" s="5">
+        <v>164</v>
+      </c>
+      <c r="G8" s="37">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9">
+        <v>45</v>
+      </c>
+      <c r="E9" s="10">
+        <v>9</v>
+      </c>
+      <c r="F9" s="11">
+        <v>7</v>
+      </c>
+      <c r="G9" s="37">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1011</v>
+      </c>
+      <c r="E10" s="13">
+        <v>123</v>
+      </c>
+      <c r="F10" s="14">
+        <v>100</v>
+      </c>
+      <c r="G10" s="37">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D11" s="15">
+        <v>24</v>
+      </c>
+      <c r="E11" s="16">
+        <v>11</v>
+      </c>
+      <c r="F11" s="17">
+        <v>9</v>
+      </c>
+      <c r="G11" s="37">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="18">
+        <v>2130</v>
+      </c>
+      <c r="E12" s="19">
+        <v>309</v>
+      </c>
+      <c r="F12" s="20">
+        <v>274</v>
+      </c>
+      <c r="G12" s="37">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="21">
+        <v>2063</v>
+      </c>
+      <c r="E13" s="22">
+        <v>348</v>
+      </c>
+      <c r="F13" s="23">
+        <v>319</v>
+      </c>
+      <c r="G13" s="37">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="24">
+        <v>2653</v>
+      </c>
+      <c r="E14" s="25">
+        <v>329</v>
+      </c>
+      <c r="F14" s="26">
+        <v>295</v>
+      </c>
+      <c r="G14" s="37">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="27">
+        <v>5</v>
+      </c>
+      <c r="E15" s="28">
+        <v>1</v>
+      </c>
+      <c r="F15" s="29">
+        <v>1</v>
+      </c>
+      <c r="G15" s="37">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="9">
-        <v>1927</v>
-      </c>
-      <c r="E8" s="7">
-        <v>200</v>
-      </c>
-      <c r="F8" s="7">
-        <v>164</v>
-      </c>
-      <c r="G8" s="40">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="D16" s="30">
+        <v>4</v>
+      </c>
+      <c r="E16" s="31">
+        <v>2</v>
+      </c>
+      <c r="F16" s="32">
+        <v>2</v>
+      </c>
+      <c r="G16" s="37">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="12">
-        <v>45</v>
-      </c>
-      <c r="E9" s="13">
-        <v>9</v>
-      </c>
-      <c r="F9" s="14">
-        <v>7</v>
-      </c>
-      <c r="G9" s="40">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="15">
-        <v>1011</v>
-      </c>
-      <c r="E10" s="16">
-        <v>123</v>
-      </c>
-      <c r="F10" s="17">
-        <v>100</v>
-      </c>
-      <c r="G10" s="40">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="18">
+      <c r="B17" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="19">
-        <v>11</v>
-      </c>
-      <c r="F11" s="20">
-        <v>9</v>
-      </c>
-      <c r="G11" s="40">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="21">
-        <v>2130</v>
-      </c>
-      <c r="E12" s="22">
-        <v>309</v>
-      </c>
-      <c r="F12" s="23">
-        <v>274</v>
-      </c>
-      <c r="G12" s="40">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="24">
-        <v>2063</v>
-      </c>
-      <c r="E13" s="25">
-        <v>348</v>
-      </c>
-      <c r="F13" s="26">
-        <v>319</v>
-      </c>
-      <c r="G13" s="40">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="27">
-        <v>2653</v>
-      </c>
-      <c r="E14" s="28">
-        <v>329</v>
-      </c>
-      <c r="F14" s="29">
-        <v>295</v>
-      </c>
-      <c r="G14" s="40">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="30">
-        <v>5</v>
-      </c>
-      <c r="E15" s="31">
-        <v>1</v>
-      </c>
-      <c r="F15" s="32">
-        <v>1</v>
-      </c>
-      <c r="G15" s="40">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="33">
-        <v>4</v>
-      </c>
-      <c r="E16" s="34">
-        <v>2</v>
-      </c>
-      <c r="F16" s="35">
-        <v>2</v>
-      </c>
-      <c r="G16" s="40">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="37">
+      <c r="D17" s="34">
         <v>44</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="35">
         <v>30</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="36">
         <v>30</v>
       </c>
-      <c r="G17" s="40">
-        <v>0.75</v>
+      <c r="G17" s="37">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/api/placeholders/RifResistanceRate.xlsx
+++ b/api/placeholders/RifResistanceRate.xlsx
@@ -26,9 +26,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
-    <t>Deployment Name</t>
-  </si>
-  <si>
     <t>Total Tests</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>Wooster Hospital</t>
+  </si>
+  <si>
+    <t>Devices</t>
   </si>
 </sst>
 </file>
@@ -772,14 +772,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
@@ -790,36 +790,36 @@
     </row>
     <row r="7" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>1</v>
-      </c>
       <c r="E7" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="G7" s="38" t="s">
         <v>4</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D8" s="6">
         <v>1927</v>
@@ -836,13 +836,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="D9" s="9">
         <v>45</v>
@@ -859,13 +859,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>16</v>
       </c>
       <c r="D10" s="12">
         <v>1011</v>
@@ -882,13 +882,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="33" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>19</v>
       </c>
       <c r="D11" s="15">
         <v>24</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>21</v>
       </c>
       <c r="D12" s="18">
         <v>2130</v>
@@ -928,13 +928,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>10</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="21">
         <v>2063</v>
@@ -951,13 +951,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>24</v>
       </c>
       <c r="D14" s="24">
         <v>2653</v>
@@ -974,13 +974,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="33" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>27</v>
       </c>
       <c r="D15" s="27">
         <v>5</v>
@@ -997,13 +997,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>29</v>
       </c>
       <c r="D16" s="30">
         <v>4</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="34">
         <v>44</v>
